--- a/AAII_Financials/Quarterly/NRSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NRSN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
   <si>
     <t>NRSN</t>
   </si>
@@ -656,72 +656,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -734,8 +735,11 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -784,8 +788,11 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -834,8 +841,11 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -884,8 +894,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,44 +917,45 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E12" s="3">
         <v>1900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3100</v>
-      </c>
-      <c r="K12" s="3">
-        <v>2500</v>
       </c>
       <c r="L12" s="3">
         <v>2500</v>
       </c>
       <c r="M12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N12" s="3">
         <v>500</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -954,8 +968,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,8 +1021,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1054,8 +1074,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1104,8 +1127,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,44 +1147,45 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E17" s="3">
         <v>3500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>700</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1171,8 +1198,11 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,35 +1210,35 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-700</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1221,8 +1251,11 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,8 +1274,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1250,34 +1284,34 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1500</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1291,8 +1325,11 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1308,24 +1345,24 @@
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3">
         <v>-3400</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
         <v>-4000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-2800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1341,8 +1378,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1391,44 +1431,47 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-600</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1441,8 +1484,11 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1491,8 +1537,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,44 +1590,47 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-600</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1591,44 +1643,47 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-600</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1641,8 +1696,11 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1749,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1741,8 +1802,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1855,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,8 +1908,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1850,34 +1920,34 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1500</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -1891,44 +1961,47 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-600</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1941,8 +2014,11 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,44 +2067,47 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-600</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2041,49 +2120,52 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2096,8 +2178,11 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2201,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,38 +2222,39 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E41" s="3">
         <v>7100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1000</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2186,32 +2273,35 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>3100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5000</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2227,8 +2317,8 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2236,37 +2326,40 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>300</v>
+      </c>
+      <c r="E43" s="3">
         <v>400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
+      <c r="L43" s="3">
+        <v>0</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
@@ -2286,8 +2379,11 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2336,8 +2432,11 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2357,13 +2456,13 @@
         <v>0</v>
       </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
+      <c r="K45" s="3">
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
@@ -2380,44 +2479,47 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E46" s="3">
         <v>7600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2436,8 +2538,11 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2486,8 +2591,11 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2510,13 +2618,13 @@
         <v>300</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
+      <c r="L48" s="3">
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
@@ -2536,8 +2644,11 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2586,8 +2697,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2750,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,8 +2803,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2706,17 +2826,17 @@
       <c r="H52" s="3">
         <v>0</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="I52" s="3">
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
@@ -2736,8 +2856,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,38 +2909,41 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E54" s="3">
         <v>7900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1100</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,8 +2962,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +2985,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,37 +3006,38 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
       <c r="K57" s="3">
         <v>0</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
+      <c r="L57" s="3">
+        <v>0</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
@@ -2926,8 +3057,11 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2976,8 +3110,11 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2985,29 +3122,29 @@
         <v>1900</v>
       </c>
       <c r="E59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F59" s="3">
         <v>1400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>600</v>
       </c>
       <c r="H59" s="3">
         <v>600</v>
       </c>
       <c r="I59" s="3">
+        <v>600</v>
+      </c>
+      <c r="J59" s="3">
         <v>1000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3026,38 +3163,41 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E60" s="3">
         <v>3000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>100</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3076,8 +3216,11 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3091,7 +3234,7 @@
         <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
         <v>200</v>
@@ -3100,7 +3243,7 @@
         <v>200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3126,35 +3269,38 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E62" s="3">
         <v>6300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1800</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3170,14 +3316,17 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3375,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3428,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,38 +3481,41 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E66" s="3">
         <v>9400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3376,8 +3534,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3557,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3608,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3661,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3546,8 +3714,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,38 +3767,41 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-29900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-24700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-20800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-17600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-14600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-11200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7500</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3646,8 +3820,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +3873,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +3926,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,38 +3979,41 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>900</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3846,8 +4032,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,49 +4085,52 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3951,44 +4143,47 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-600</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4001,8 +4196,11 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,8 +4219,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4038,23 +4237,23 @@
       <c r="G83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -4071,8 +4270,11 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4323,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4376,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4429,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4482,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,8 +4535,11 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4338,23 +4555,23 @@
       <c r="G89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3">
         <v>-4300</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
+      <c r="M89" s="3">
+        <v>0</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
@@ -4371,8 +4588,11 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,8 +4611,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4423,8 +4644,8 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
@@ -4441,8 +4662,11 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4715,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,8 +4768,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4558,23 +4788,23 @@
       <c r="G94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3">
         <v>-6000</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
@@ -4591,8 +4821,11 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,8 +4844,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4661,8 +4895,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +4948,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5001,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,8 +5054,11 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4828,23 +5074,23 @@
       <c r="G100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
         <v>3700</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
+      <c r="M100" s="3">
+        <v>0</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
@@ -4861,8 +5107,11 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4878,41 +5127,44 @@
       <c r="G101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4928,23 +5180,23 @@
       <c r="G102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H102" s="3">
+      <c r="H102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I102" s="3">
         <v>-6700</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>0</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
@@ -4959,6 +5211,9 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NRSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NRSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="92">
   <si>
     <t>NRSN</t>
   </si>
@@ -656,76 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -738,8 +738,11 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -791,8 +794,11 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -844,8 +850,11 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -897,8 +906,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,47 +930,48 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3100</v>
-      </c>
-      <c r="L12" s="3">
-        <v>2500</v>
       </c>
       <c r="M12" s="3">
         <v>2500</v>
       </c>
       <c r="N12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O12" s="3">
         <v>500</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -971,8 +984,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,8 +1040,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1077,8 +1096,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1130,8 +1152,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,47 +1173,48 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E17" s="3">
         <v>2900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>700</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1201,8 +1227,11 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1210,38 +1239,38 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-700</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1254,8 +1283,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,8 +1307,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1284,37 +1317,37 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1500</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1328,8 +1361,11 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1348,24 +1384,24 @@
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3">
         <v>-3400</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>-4000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-2800</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1381,8 +1417,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1434,47 +1473,50 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E23" s="3">
         <v>800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-600</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1487,8 +1529,11 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1540,8 +1585,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,47 +1641,50 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E26" s="3">
         <v>800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-600</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1646,47 +1697,50 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E27" s="3">
         <v>800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-600</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1699,8 +1753,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1809,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1865,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1921,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,8 +1977,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1920,37 +1989,37 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F32" s="3">
         <v>1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1500</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -1964,47 +2033,50 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E33" s="3">
         <v>800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-600</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2017,8 +2089,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,47 +2145,50 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E35" s="3">
         <v>800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-600</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,52 +2201,55 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2181,8 +2262,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2286,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,41 +2308,42 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E41" s="3">
         <v>4800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1000</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2276,35 +2362,38 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>3100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5000</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2320,8 +2409,8 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2329,40 +2418,43 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>300</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
+      <c r="M43" s="3">
+        <v>0</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
@@ -2382,8 +2474,11 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2435,8 +2530,11 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2459,13 +2557,13 @@
         <v>0</v>
       </c>
       <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
+      <c r="L45" s="3">
+        <v>0</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
@@ -2482,47 +2580,50 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
+      <c r="R45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E46" s="3">
         <v>5100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1000</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2541,8 +2642,11 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2594,13 +2698,16 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E48" s="3">
         <v>300</v>
@@ -2621,13 +2728,13 @@
         <v>300</v>
       </c>
       <c r="K48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
+      <c r="M48" s="3">
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
@@ -2647,8 +2754,11 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2700,8 +2810,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2866,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,8 +2922,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2829,17 +2948,17 @@
       <c r="I52" s="3">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+      <c r="J52" s="3">
+        <v>0</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
@@ -2859,8 +2978,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,41 +3034,44 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E54" s="3">
         <v>5400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1100</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,8 +3090,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3114,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,40 +3136,41 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
+      <c r="M57" s="3">
+        <v>0</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
@@ -3060,8 +3190,11 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3113,41 +3246,44 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="E59" s="3">
         <v>1900</v>
       </c>
       <c r="F59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G59" s="3">
         <v>1400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>600</v>
       </c>
       <c r="I59" s="3">
         <v>600</v>
       </c>
       <c r="J59" s="3">
+        <v>600</v>
+      </c>
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3166,41 +3302,44 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E60" s="3">
         <v>2800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>100</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3219,8 +3358,11 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3237,7 +3379,7 @@
         <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
         <v>200</v>
@@ -3246,7 +3388,7 @@
         <v>200</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -3272,38 +3414,41 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E62" s="3">
         <v>2700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1800</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3319,14 +3464,17 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3526,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3582,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,41 +3638,44 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E66" s="3">
         <v>5600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>100</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3537,8 +3694,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3718,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3772,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3828,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3717,8 +3884,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,41 +3940,44 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-32100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-29100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-29900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-24700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-20800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-17600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-14600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-11200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-8400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-7500</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3823,8 +3996,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4052,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4108,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,41 +4164,44 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>900</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4035,8 +4220,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,52 +4276,55 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4146,47 +4337,50 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E81" s="3">
         <v>800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-600</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4199,8 +4393,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,8 +4417,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4240,23 +4438,23 @@
       <c r="H83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
@@ -4273,8 +4471,11 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4527,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4583,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4639,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4695,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,8 +4751,11 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4558,23 +4774,23 @@
       <c r="H89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>-4300</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
+      <c r="N89" s="3">
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
@@ -4591,8 +4807,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,8 +4831,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4647,8 +4867,8 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
@@ -4665,8 +4885,11 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +4941,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,8 +4997,11 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4791,23 +5020,23 @@
       <c r="H94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>-6000</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -4824,8 +5053,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5077,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4898,8 +5131,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5187,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5243,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,8 +5299,11 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5077,23 +5322,23 @@
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>3700</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
@@ -5110,8 +5355,11 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5130,41 +5378,44 @@
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5183,23 +5434,23 @@
       <c r="H102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I102" s="3">
+      <c r="I102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J102" s="3">
         <v>-6700</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
@@ -5214,6 +5465,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NRSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NRSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="92">
   <si>
     <t>NRSN</t>
   </si>
@@ -656,79 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -741,8 +742,11 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -797,8 +801,11 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -853,8 +860,11 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -909,8 +919,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -931,50 +944,51 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="E12" s="3">
         <v>1600</v>
       </c>
       <c r="F12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G12" s="3">
         <v>1900</v>
       </c>
-      <c r="G12" s="3">
-        <v>2100</v>
-      </c>
       <c r="H12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I12" s="3">
         <v>1500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3100</v>
-      </c>
-      <c r="M12" s="3">
-        <v>2500</v>
       </c>
       <c r="N12" s="3">
         <v>2500</v>
       </c>
       <c r="O12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="P12" s="3">
         <v>500</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,8 +1001,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1043,8 +1060,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1099,8 +1119,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1155,8 +1178,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1174,50 +1200,51 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J17" s="3">
         <v>3300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="K17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M17" s="3">
+        <v>5600</v>
+      </c>
+      <c r="N17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="O17" s="3">
         <v>2900</v>
       </c>
-      <c r="F17" s="3">
-        <v>3500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>3600</v>
-      </c>
-      <c r="H17" s="3">
-        <v>3400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>3300</v>
-      </c>
-      <c r="J17" s="3">
-        <v>3600</v>
-      </c>
-      <c r="K17" s="3">
-        <v>3300</v>
-      </c>
-      <c r="L17" s="3">
-        <v>5600</v>
-      </c>
-      <c r="M17" s="3">
-        <v>3100</v>
-      </c>
-      <c r="N17" s="3">
-        <v>2900</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>700</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,8 +1257,11 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1239,41 +1269,41 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-3600</v>
       </c>
-      <c r="H18" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
         <v>-3300</v>
       </c>
-      <c r="J18" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-700</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1286,8 +1316,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1308,8 +1341,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1317,40 +1351,40 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>3700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1700</v>
       </c>
-      <c r="G20" s="3">
-        <v>-200</v>
-      </c>
       <c r="H20" s="3">
+        <v>100</v>
+      </c>
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1500</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1364,8 +1398,11 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1378,8 +1415,8 @@
       <c r="F21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
+      <c r="G21" s="3">
+        <v>-5200</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1387,24 +1424,24 @@
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
         <v>-3400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-4000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-2800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1420,8 +1457,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1476,50 +1516,53 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F23" s="3">
+        <v>800</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="J23" s="3">
         <v>-3000</v>
       </c>
-      <c r="E23" s="3">
-        <v>800</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-600</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1532,8 +1575,11 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1588,8 +1634,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1644,50 +1693,53 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F26" s="3">
+        <v>800</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="J26" s="3">
         <v>-3000</v>
       </c>
-      <c r="E26" s="3">
-        <v>800</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-600</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1700,50 +1752,53 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F27" s="3">
+        <v>800</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="J27" s="3">
         <v>-3000</v>
       </c>
-      <c r="E27" s="3">
-        <v>800</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-600</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1756,8 +1811,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1812,8 +1870,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1868,8 +1929,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1924,8 +1988,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1980,8 +2047,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1989,40 +2059,40 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1700</v>
       </c>
-      <c r="G32" s="3">
-        <v>200</v>
-      </c>
       <c r="H32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1500</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -2036,50 +2106,53 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F33" s="3">
+        <v>800</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="J33" s="3">
         <v>-3000</v>
       </c>
-      <c r="E33" s="3">
-        <v>800</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-600</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2092,8 +2165,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2148,50 +2224,53 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F35" s="3">
+        <v>800</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="J35" s="3">
         <v>-3000</v>
       </c>
-      <c r="E35" s="3">
-        <v>800</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-600</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2204,55 +2283,58 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2265,8 +2347,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2287,8 +2372,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2309,44 +2395,45 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>700</v>
+      </c>
+      <c r="E41" s="3">
         <v>2600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1000</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2365,38 +2452,41 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>3100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5000</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2412,8 +2502,8 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2421,43 +2511,46 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
+      <c r="N43" s="3">
+        <v>0</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
@@ -2477,8 +2570,11 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2533,8 +2629,11 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2560,13 +2659,13 @@
         <v>0</v>
       </c>
       <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
+      <c r="M45" s="3">
+        <v>0</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
@@ -2583,50 +2682,53 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E46" s="3">
         <v>2900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1000</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,8 +2747,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2701,8 +2806,11 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2710,7 +2818,7 @@
         <v>200</v>
       </c>
       <c r="E48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F48" s="3">
         <v>300</v>
@@ -2731,13 +2839,13 @@
         <v>300</v>
       </c>
       <c r="L48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
+      <c r="N48" s="3">
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
@@ -2757,8 +2865,11 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2813,8 +2924,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2869,8 +2983,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,8 +3042,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2951,17 +3071,17 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
@@ -2981,8 +3101,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3037,44 +3160,47 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E54" s="3">
         <v>3200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1100</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3219,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3115,8 +3244,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3137,43 +3267,44 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
+      <c r="N57" s="3">
+        <v>0</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
@@ -3193,8 +3324,11 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3249,44 +3383,47 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E59" s="3">
         <v>2000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>1900</v>
       </c>
       <c r="F59" s="3">
         <v>1900</v>
       </c>
       <c r="G59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H59" s="3">
         <v>1400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>600</v>
       </c>
       <c r="J59" s="3">
         <v>600</v>
       </c>
       <c r="K59" s="3">
+        <v>600</v>
+      </c>
+      <c r="L59" s="3">
         <v>1000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3305,44 +3442,47 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E60" s="3">
         <v>3500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>100</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3361,8 +3501,11 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3382,7 +3525,7 @@
         <v>100</v>
       </c>
       <c r="I61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
         <v>200</v>
@@ -3391,7 +3534,7 @@
         <v>200</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -3417,41 +3560,44 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1500</v>
+        <v>3800</v>
       </c>
       <c r="E62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F62" s="3">
         <v>2700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1800</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3467,14 +3613,17 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3529,8 +3678,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3585,8 +3737,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3641,44 +3796,47 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5100</v>
+        <v>8400</v>
       </c>
       <c r="E66" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F66" s="3">
         <v>5600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>100</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3697,8 +3855,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3719,8 +3880,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3775,8 +3937,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3831,8 +3996,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3887,8 +4055,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3943,44 +4114,47 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-32100</v>
+        <v>-31500</v>
       </c>
       <c r="E72" s="3">
+        <v>-26100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-29100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-29900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-24700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-20800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-17600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-14600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-11200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-8400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7500</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3999,8 +4173,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4055,8 +4232,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4111,8 +4291,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4167,44 +4350,47 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-1900</v>
+        <v>-7000</v>
       </c>
       <c r="E76" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F76" s="3">
         <v>-200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>900</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4223,8 +4409,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,55 +4468,58 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4340,50 +4532,53 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F81" s="3">
+        <v>800</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="J81" s="3">
         <v>-3000</v>
       </c>
-      <c r="E81" s="3">
-        <v>800</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-600</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4396,8 +4591,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4418,8 +4616,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4432,8 +4631,8 @@
       <c r="F83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
+      <c r="G83" s="3">
+        <v>0</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -4441,23 +4640,23 @@
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
@@ -4474,8 +4673,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4530,8 +4732,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4586,8 +4791,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4642,8 +4850,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4698,8 +4909,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4754,8 +4968,11 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4768,8 +4985,8 @@
       <c r="F89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
+      <c r="G89" s="3">
+        <v>-4100</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -4777,23 +4994,23 @@
       <c r="I89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
         <v>-4300</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
+      <c r="O89" s="3">
+        <v>0</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
@@ -4810,8 +5027,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4832,8 +5052,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4870,8 +5091,8 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -4888,8 +5109,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4944,8 +5168,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5000,8 +5227,11 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5014,8 +5244,8 @@
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+      <c r="G94" s="3">
+        <v>3500</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -5023,23 +5253,23 @@
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
         <v>-6000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
@@ -5056,8 +5286,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5078,8 +5311,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5134,8 +5368,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5190,8 +5427,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5246,8 +5486,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5302,8 +5545,11 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5316,8 +5562,8 @@
       <c r="F100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
+      <c r="G100" s="3">
+        <v>4100</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -5325,23 +5571,23 @@
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>3700</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
@@ -5358,8 +5604,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5372,8 +5621,8 @@
       <c r="F101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -5381,41 +5630,44 @@
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5428,8 +5680,8 @@
       <c r="F102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
+      <c r="G102" s="3">
+        <v>3500</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>
@@ -5437,23 +5689,23 @@
       <c r="I102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J102" s="3">
+      <c r="J102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K102" s="3">
         <v>-6700</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
+      <c r="O102" s="3">
+        <v>0</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
@@ -5468,6 +5720,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NRSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NRSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="92">
   <si>
     <t>NRSN</t>
   </si>
@@ -656,83 +656,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -745,31 +746,34 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -804,8 +808,11 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -863,8 +870,11 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -922,8 +932,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,53 +958,54 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E12" s="3">
         <v>1900</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1600</v>
       </c>
       <c r="F12" s="3">
         <v>1600</v>
       </c>
       <c r="G12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I12" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J12" s="3">
+        <v>700</v>
+      </c>
+      <c r="K12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L12" s="3">
         <v>1900</v>
       </c>
-      <c r="H12" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1700</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1900</v>
-      </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3100</v>
-      </c>
-      <c r="N12" s="3">
-        <v>2500</v>
       </c>
       <c r="O12" s="3">
         <v>2500</v>
       </c>
       <c r="P12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Q12" s="3">
         <v>500</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1004,8 +1018,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,31 +1080,34 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1122,8 +1142,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1181,8 +1204,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,8 +1227,9 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1210,44 +1237,44 @@
         <v>3000</v>
       </c>
       <c r="E17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F17" s="3">
         <v>2000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2900</v>
       </c>
-      <c r="G17" s="3">
-        <v>3500</v>
-      </c>
       <c r="H17" s="3">
-        <v>3000</v>
+        <v>2700</v>
       </c>
       <c r="I17" s="3">
-        <v>3400</v>
+        <v>3600</v>
       </c>
       <c r="J17" s="3">
+        <v>400</v>
+      </c>
+      <c r="K17" s="3">
         <v>3300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>700</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1260,53 +1287,56 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-3000</v>
       </c>
       <c r="E18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-3500</v>
-      </c>
       <c r="H18" s="3">
-        <v>-3000</v>
+        <v>-2700</v>
       </c>
       <c r="I18" s="3">
-        <v>-3400</v>
+        <v>-3600</v>
       </c>
       <c r="J18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-3300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-700</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1319,8 +1349,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,52 +1375,53 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
-        <v>3700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>300</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>200</v>
-      </c>
-      <c r="J20" s="3">
-        <v>300</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
+        <v>500</v>
+      </c>
+      <c r="N20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>500</v>
-      </c>
-      <c r="M20" s="3">
-        <v>1500</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1401,50 +1435,53 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-300</v>
       </c>
       <c r="G21" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>-3400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-4000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-2800</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1460,31 +1497,34 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>-2200</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>-2200</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1519,53 +1559,56 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5400</v>
       </c>
-      <c r="E23" s="3">
-        <v>-2000</v>
-      </c>
       <c r="F23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G23" s="3">
         <v>800</v>
       </c>
-      <c r="G23" s="3">
-        <v>-5200</v>
-      </c>
       <c r="H23" s="3">
-        <v>-2900</v>
+        <v>-2700</v>
       </c>
       <c r="I23" s="3">
-        <v>-3200</v>
+        <v>-3900</v>
       </c>
       <c r="J23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K23" s="3">
         <v>-3000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-600</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,31 +1621,34 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1637,8 +1683,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,53 +1745,56 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5400</v>
       </c>
-      <c r="E26" s="3">
-        <v>-2000</v>
-      </c>
       <c r="F26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G26" s="3">
         <v>800</v>
       </c>
-      <c r="G26" s="3">
-        <v>-5200</v>
-      </c>
       <c r="H26" s="3">
-        <v>-2900</v>
+        <v>-2700</v>
       </c>
       <c r="I26" s="3">
-        <v>-3200</v>
+        <v>-3900</v>
       </c>
       <c r="J26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K26" s="3">
         <v>-3000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-600</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1755,53 +1807,56 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5400</v>
       </c>
-      <c r="E27" s="3">
-        <v>-2000</v>
-      </c>
       <c r="F27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G27" s="3">
         <v>800</v>
       </c>
-      <c r="G27" s="3">
-        <v>-5200</v>
-      </c>
       <c r="H27" s="3">
-        <v>-2900</v>
+        <v>-2700</v>
       </c>
       <c r="I27" s="3">
-        <v>-3200</v>
+        <v>-3900</v>
       </c>
       <c r="J27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K27" s="3">
         <v>-3000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-600</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1814,8 +1869,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +1993,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,52 +2117,55 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -2109,53 +2179,56 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5400</v>
       </c>
-      <c r="E33" s="3">
-        <v>-2000</v>
-      </c>
       <c r="F33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G33" s="3">
         <v>800</v>
       </c>
-      <c r="G33" s="3">
-        <v>-5200</v>
-      </c>
       <c r="H33" s="3">
-        <v>-2900</v>
+        <v>-2700</v>
       </c>
       <c r="I33" s="3">
-        <v>-3200</v>
+        <v>-3900</v>
       </c>
       <c r="J33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K33" s="3">
         <v>-3000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-600</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2168,8 +2241,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,53 +2303,56 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5400</v>
       </c>
-      <c r="E35" s="3">
-        <v>-2000</v>
-      </c>
       <c r="F35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G35" s="3">
         <v>800</v>
       </c>
-      <c r="G35" s="3">
-        <v>-5200</v>
-      </c>
       <c r="H35" s="3">
-        <v>-2900</v>
+        <v>-2700</v>
       </c>
       <c r="I35" s="3">
-        <v>-3200</v>
+        <v>-3900</v>
       </c>
       <c r="J35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K35" s="3">
         <v>-3000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-600</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2286,58 +2365,61 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2350,8 +2432,11 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,47 +2482,48 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E41" s="3">
         <v>700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1000</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2455,41 +2542,44 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
+      <c r="F42" s="3">
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>3100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5000</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2505,8 +2595,8 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -2514,8 +2604,11 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2523,37 +2616,37 @@
         <v>400</v>
       </c>
       <c r="E43" s="3">
+        <v>400</v>
+      </c>
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
+        <v>100</v>
+      </c>
+      <c r="K43" s="3">
+        <v>400</v>
+      </c>
+      <c r="L43" s="3">
+        <v>700</v>
+      </c>
+      <c r="M43" s="3">
+        <v>200</v>
+      </c>
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
-        <v>400</v>
-      </c>
-      <c r="K43" s="3">
-        <v>700</v>
-      </c>
-      <c r="L43" s="3">
-        <v>200</v>
-      </c>
-      <c r="M43" s="3">
-        <v>300</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
+      <c r="O43" s="3">
+        <v>0</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
@@ -2573,31 +2666,34 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2632,8 +2728,11 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2662,13 +2761,13 @@
         <v>0</v>
       </c>
       <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
+      <c r="N45" s="3">
+        <v>0</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
@@ -2685,53 +2784,56 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1000</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2750,31 +2852,34 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2809,8 +2914,11 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2821,7 +2929,7 @@
         <v>200</v>
       </c>
       <c r="F48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G48" s="3">
         <v>300</v>
@@ -2842,13 +2950,13 @@
         <v>300</v>
       </c>
       <c r="M48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
+      <c r="O48" s="3">
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
@@ -2868,8 +2976,11 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2927,8 +3038,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,8 +3162,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3074,17 +3194,17 @@
       <c r="K52" s="3">
         <v>0</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
+      <c r="L52" s="3">
+        <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
@@ -3104,8 +3224,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,47 +3286,50 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1100</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3222,8 +3348,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,46 +3398,47 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
       <c r="N57" s="3">
         <v>0</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
+      <c r="O57" s="3">
+        <v>0</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
@@ -3327,8 +3458,11 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3339,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
@@ -3351,7 +3485,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3386,47 +3520,50 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2200</v>
       </c>
-      <c r="E59" s="3">
-        <v>2000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1900</v>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G59" s="3">
         <v>1900</v>
       </c>
       <c r="H59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I59" s="3">
         <v>1400</v>
       </c>
-      <c r="I59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>600</v>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>600</v>
       </c>
       <c r="L59" s="3">
+        <v>600</v>
+      </c>
+      <c r="M59" s="3">
         <v>1000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3445,47 +3582,50 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E60" s="3">
         <v>4500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>100</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3504,13 +3644,16 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
         <v>100</v>
@@ -3528,7 +3671,7 @@
         <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K61" s="3">
         <v>200</v>
@@ -3537,7 +3680,7 @@
         <v>200</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -3563,44 +3706,47 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3">
         <v>3800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="I62" s="3">
-        <v>200</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1800</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3616,14 +3762,17 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,47 +3954,50 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E66" s="3">
         <v>8400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2400</v>
       </c>
-      <c r="I66" s="3">
-        <v>2100</v>
-      </c>
       <c r="J66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K66" s="3">
         <v>1400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>100</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3858,8 +4016,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4058,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,47 +4288,50 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-31500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-26100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-29100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-29900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-24700</v>
       </c>
-      <c r="I72" s="3">
-        <v>-20800</v>
-      </c>
       <c r="J72" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="K72" s="3">
         <v>-17600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-14600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-11200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-8400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7500</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4176,8 +4350,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,47 +4536,50 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-7000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2900</v>
       </c>
-      <c r="I76" s="3">
-        <v>5600</v>
-      </c>
       <c r="J76" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K76" s="3">
         <v>7800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>900</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4412,8 +4598,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,58 +4660,61 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4535,53 +4727,56 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5400</v>
       </c>
-      <c r="E81" s="3">
-        <v>-2000</v>
-      </c>
       <c r="F81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G81" s="3">
         <v>800</v>
       </c>
-      <c r="G81" s="3">
-        <v>-5200</v>
-      </c>
       <c r="H81" s="3">
-        <v>-2900</v>
+        <v>-2700</v>
       </c>
       <c r="I81" s="3">
-        <v>-3200</v>
+        <v>-3900</v>
       </c>
       <c r="J81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K81" s="3">
         <v>-3000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-600</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4594,8 +4789,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,8 +4815,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4631,8 +4830,8 @@
       <c r="F83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -4643,23 +4842,23 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
@@ -4676,8 +4875,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,8 +5185,11 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4985,8 +5202,8 @@
       <c r="F89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G89" s="3">
-        <v>-4100</v>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -4997,23 +5214,23 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>-4300</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O89" s="3">
         <v>0</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
+      <c r="P89" s="3">
+        <v>0</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
@@ -5030,8 +5247,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,31 +5273,32 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5094,8 +5315,8 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -5112,8 +5333,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,8 +5457,11 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5244,8 +5474,8 @@
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="3">
-        <v>3500</v>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -5256,23 +5486,23 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>-6000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -5289,8 +5519,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,31 +5545,32 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5371,8 +5605,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,8 +5791,11 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5562,8 +5808,8 @@
       <c r="F100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G100" s="3">
-        <v>4100</v>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -5574,23 +5820,23 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>3700</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
@@ -5607,8 +5853,11 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5621,8 +5870,8 @@
       <c r="F101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -5633,82 +5882,85 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>3500</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3">
         <v>-6700</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
+      <c r="P102" s="3">
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
@@ -5723,6 +5975,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NRSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NRSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="92">
   <si>
     <t>NRSN</t>
   </si>
@@ -656,87 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -749,8 +750,11 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -775,8 +779,8 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -811,8 +815,11 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -873,8 +880,11 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -935,8 +945,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,56 +972,57 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E12" s="3">
         <v>1600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1900</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1600</v>
       </c>
       <c r="G12" s="3">
         <v>1600</v>
       </c>
       <c r="H12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I12" s="3">
         <v>1700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3100</v>
-      </c>
-      <c r="O12" s="3">
-        <v>2500</v>
       </c>
       <c r="P12" s="3">
         <v>2500</v>
       </c>
       <c r="Q12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R12" s="3">
         <v>500</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1021,8 +1035,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,8 +1100,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1109,8 +1129,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1145,8 +1165,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,56 +1254,57 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3000</v>
+        <v>2100</v>
       </c>
       <c r="E17" s="3">
         <v>3000</v>
       </c>
       <c r="F17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G17" s="3">
         <v>2000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>700</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1290,56 +1317,59 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3000</v>
+        <v>-2100</v>
       </c>
       <c r="E18" s="3">
         <v>-3000</v>
       </c>
       <c r="F18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="G18" s="3">
         <v>-2000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-700</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1352,8 +1382,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,8 +1409,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1387,44 +1421,44 @@
       <c r="E20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1800</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1500</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
@@ -1438,53 +1472,56 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-3000</v>
+        <v>-2100</v>
       </c>
       <c r="E21" s="3">
         <v>-3000</v>
       </c>
       <c r="F21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="G21" s="3">
         <v>-300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-3400</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-4000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1500,35 +1537,38 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
         <v>-2200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>-2200</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>-100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>-100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1562,56 +1602,59 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-600</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1624,8 +1667,11 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1650,8 +1696,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1686,8 +1732,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,56 +1797,59 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-600</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1810,56 +1862,59 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-600</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1872,8 +1927,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,8 +2187,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2131,44 +2201,44 @@
       <c r="E32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
         <v>1800</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1500</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
@@ -2182,56 +2252,59 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-600</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2244,8 +2317,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,56 +2382,59 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-600</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2368,61 +2447,64 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2435,8 +2517,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,50 +2569,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1000</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2632,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2566,23 +2656,23 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>3100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5000</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2598,8 +2688,8 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2607,8 +2697,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2619,37 +2712,37 @@
         <v>400</v>
       </c>
       <c r="F43" s="3">
+        <v>400</v>
+      </c>
+      <c r="G43" s="3">
         <v>200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
+      <c r="P43" s="3">
+        <v>0</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
@@ -2669,8 +2762,11 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2695,8 +2791,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2731,8 +2827,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2764,13 +2863,13 @@
         <v>0</v>
       </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
+      <c r="O45" s="3">
+        <v>0</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
@@ -2787,56 +2886,59 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U45" s="3">
-        <v>0</v>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1000</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,8 +2957,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2881,8 +2986,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2917,8 +3022,11 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2932,7 +3040,7 @@
         <v>200</v>
       </c>
       <c r="G48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H48" s="3">
         <v>300</v>
@@ -2953,13 +3061,13 @@
         <v>300</v>
       </c>
       <c r="N48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
+      <c r="P48" s="3">
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
@@ -2979,8 +3087,11 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,8 +3282,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3197,17 +3317,17 @@
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
@@ -3227,8 +3347,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,50 +3412,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1100</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,49 +3529,50 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
       <c r="O57" s="3">
         <v>0</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
+      <c r="P57" s="3">
+        <v>0</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
@@ -3461,8 +3592,11 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3473,11 +3607,11 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>100</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
@@ -3485,11 +3619,11 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -3523,50 +3657,53 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E59" s="3">
         <v>2000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2200</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1900</v>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3">
         <v>1900</v>
       </c>
       <c r="I59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J59" s="3">
         <v>1400</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3">
-        <v>600</v>
+      <c r="K59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L59" s="3">
         <v>600</v>
       </c>
       <c r="M59" s="3">
+        <v>600</v>
+      </c>
+      <c r="N59" s="3">
         <v>1000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,50 +3722,53 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E60" s="3">
         <v>3500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>100</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,8 +3787,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3656,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>100</v>
@@ -3674,7 +3817,7 @@
         <v>100</v>
       </c>
       <c r="K61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L61" s="3">
         <v>200</v>
@@ -3683,7 +3826,7 @@
         <v>200</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -3709,47 +3852,50 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3">
         <v>3800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1800</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3765,14 +3911,17 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,50 +4112,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E66" s="3">
         <v>3500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>100</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,50 +4462,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-34500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-32400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-31500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-26100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-29100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-29900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-24700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-16000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-17600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-14600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-11200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-8400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7500</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4353,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,50 +4722,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-7000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>900</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4601,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,61 +4852,64 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4730,56 +4922,59 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-600</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4792,8 +4987,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,8 +5014,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4845,23 +5044,23 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
@@ -4878,8 +5077,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,8 +5402,11 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5217,23 +5434,23 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
         <v>-4300</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
+      <c r="O89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P89" s="3">
         <v>0</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
@@ -5250,8 +5467,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,8 +5494,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5300,8 +5521,8 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -5318,8 +5539,8 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -5336,8 +5557,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,8 +5687,11 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5489,23 +5719,23 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
         <v>-6000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -5522,8 +5752,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5572,8 +5806,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,8 +6037,11 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5823,23 +6069,23 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>3700</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
@@ -5856,8 +6102,11 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5885,41 +6134,44 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5944,26 +6196,26 @@
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3">
         <v>-6700</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P102" s="3">
         <v>0</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
@@ -5978,6 +6230,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NRSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NRSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="92">
   <si>
     <t>NRSN</t>
   </si>
@@ -656,91 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -753,8 +753,11 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -782,8 +785,8 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -818,8 +821,11 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -883,8 +889,11 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -948,8 +957,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,59 +985,60 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E12" s="3">
         <v>1200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1900</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1600</v>
       </c>
       <c r="H12" s="3">
         <v>1600</v>
       </c>
       <c r="I12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J12" s="3">
         <v>1700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3100</v>
-      </c>
-      <c r="P12" s="3">
-        <v>2500</v>
       </c>
       <c r="Q12" s="3">
         <v>2500</v>
       </c>
       <c r="R12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="S12" s="3">
         <v>500</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1038,8 +1051,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,8 +1119,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1132,8 +1151,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1168,8 +1187,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1233,8 +1255,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,59 +1280,60 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E17" s="3">
         <v>2100</v>
-      </c>
-      <c r="E17" s="3">
-        <v>3000</v>
       </c>
       <c r="F17" s="3">
         <v>3000</v>
       </c>
       <c r="G17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H17" s="3">
         <v>2000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>700</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1320,59 +1346,62 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2100</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-3000</v>
       </c>
       <c r="F18" s="3">
         <v>-3000</v>
       </c>
       <c r="G18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="H18" s="3">
         <v>-2000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-700</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1385,8 +1414,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,13 +1442,14 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>300</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
@@ -1424,44 +1457,44 @@
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>-1800</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1500</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
@@ -1475,8 +1508,11 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1484,47 +1520,47 @@
         <v>-2100</v>
       </c>
       <c r="E21" s="3">
-        <v>-3000</v>
+        <v>-2100</v>
       </c>
       <c r="F21" s="3">
         <v>-3000</v>
       </c>
       <c r="G21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="H21" s="3">
         <v>-300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-3400</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-4000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-2800</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,38 +1576,41 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>-2200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>-2200</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>-100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>-100</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1605,59 +1644,62 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-600</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1670,8 +1712,11 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1699,8 +1744,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1735,8 +1780,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,59 +1848,62 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-600</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1865,59 +1916,62 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-600</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1930,8 +1984,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2052,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2060,8 +2120,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2188,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,13 +2256,16 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-300</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
@@ -2204,44 +2273,44 @@
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>1800</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1500</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
@@ -2255,59 +2324,62 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-600</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2320,8 +2392,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,59 +2460,62 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-600</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2450,64 +2528,67 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2520,8 +2601,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2629,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,53 +2655,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E41" s="3">
         <v>300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1000</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2635,8 +2721,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2659,23 +2748,23 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>3100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5000</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,8 +2780,8 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2700,13 +2789,16 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E43" s="3">
         <v>400</v>
@@ -2715,37 +2807,37 @@
         <v>400</v>
       </c>
       <c r="G43" s="3">
+        <v>400</v>
+      </c>
+      <c r="H43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
+      <c r="Q43" s="3">
+        <v>0</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
@@ -2765,13 +2857,16 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>700</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>3</v>
@@ -2794,8 +2889,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2830,8 +2925,11 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2866,13 +2964,13 @@
         <v>0</v>
       </c>
       <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
+      <c r="P45" s="3">
+        <v>0</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
@@ -2889,59 +2987,62 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V45" s="3">
-        <v>0</v>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E46" s="3">
         <v>800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1000</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2960,8 +3061,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2989,8 +3093,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3025,8 +3129,11 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3043,7 +3150,7 @@
         <v>200</v>
       </c>
       <c r="H48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I48" s="3">
         <v>300</v>
@@ -3064,13 +3171,13 @@
         <v>300</v>
       </c>
       <c r="O48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
+      <c r="Q48" s="3">
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
@@ -3090,8 +3197,11 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3155,8 +3265,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3333,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,8 +3401,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3320,17 +3439,17 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
@@ -3350,8 +3469,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,53 +3537,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1100</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,8 +3605,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3633,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,52 +3659,53 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
+      <c r="Q57" s="3">
+        <v>0</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
@@ -3595,13 +3725,16 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -3610,11 +3743,11 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>100</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -3622,11 +3755,11 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3660,53 +3793,56 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>2400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2200</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1900</v>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I59" s="3">
         <v>1900</v>
       </c>
       <c r="J59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K59" s="3">
         <v>1400</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3">
-        <v>600</v>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M59" s="3">
         <v>600</v>
       </c>
       <c r="N59" s="3">
+        <v>600</v>
+      </c>
+      <c r="O59" s="3">
         <v>1000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>100</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,53 +3861,56 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E60" s="3">
         <v>3800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>100</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3790,8 +3929,11 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3802,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
         <v>100</v>
@@ -3820,7 +3962,7 @@
         <v>100</v>
       </c>
       <c r="L61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M61" s="3">
         <v>200</v>
@@ -3829,7 +3971,7 @@
         <v>200</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -3855,8 +3997,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3866,39 +4011,39 @@
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3">
         <v>3800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1800</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3914,14 +4059,17 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4133,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4201,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,53 +4269,56 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>100</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4337,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4365,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4431,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4499,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4400,8 +4567,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,53 +4635,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-36700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-34500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-32400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-31500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-26100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-29100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-29900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-24700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-16000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-17600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-14600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-11200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-8400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,8 +4703,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4771,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +4839,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,53 +4907,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-7000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4975,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,64 +5043,67 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4925,59 +5116,62 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-600</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4990,8 +5184,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,8 +5212,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5047,23 +5245,23 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
@@ -5080,8 +5278,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5346,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5414,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5482,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5550,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,8 +5618,11 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5437,23 +5653,23 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>-4300</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
+      <c r="P89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q89" s="3">
         <v>0</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
@@ -5470,8 +5686,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,8 +5714,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5524,8 +5744,8 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -5542,8 +5762,8 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -5560,8 +5780,11 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +5848,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,8 +5916,11 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5722,23 +5951,23 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>-6000</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5755,8 +5984,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,8 +6012,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5809,8 +6042,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5845,8 +6078,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6146,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6214,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,8 +6282,11 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6072,23 +6317,23 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>3700</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
@@ -6105,8 +6350,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6137,88 +6385,91 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
+      <c r="R101" s="3">
+        <v>0</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3">
         <v>-6700</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q102" s="3">
         <v>0</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
@@ -6233,6 +6484,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NRSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NRSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="92">
   <si>
     <t>NRSN</t>
   </si>
@@ -656,97 +656,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -756,8 +758,14 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -788,11 +796,11 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -824,8 +832,14 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -892,8 +906,14 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -960,8 +980,14 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -986,65 +1012,67 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F12" s="3">
         <v>1100</v>
       </c>
-      <c r="E12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3">
         <v>1600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="K12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M12" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N12" s="3">
+        <v>700</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P12" s="3">
         <v>1900</v>
       </c>
-      <c r="H12" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1700</v>
-      </c>
-      <c r="K12" s="3">
-        <v>2100</v>
-      </c>
-      <c r="L12" s="3">
-        <v>700</v>
-      </c>
-      <c r="M12" s="3">
-        <v>1700</v>
-      </c>
-      <c r="N12" s="3">
-        <v>1900</v>
-      </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>3100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>2500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>2500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>500</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,8 +1082,14 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1122,8 +1156,14 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1154,11 +1194,11 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1190,8 +1230,14 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1258,8 +1304,14 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1281,65 +1333,67 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F17" s="3">
         <v>1800</v>
       </c>
-      <c r="E17" s="3">
-        <v>2100</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3">
         <v>3000</v>
       </c>
-      <c r="G17" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3">
         <v>2000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>400</v>
-      </c>
-      <c r="M17" s="3">
-        <v>3300</v>
-      </c>
-      <c r="N17" s="3">
-        <v>3600</v>
       </c>
       <c r="O17" s="3">
         <v>3300</v>
       </c>
       <c r="P17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="R17" s="3">
         <v>5600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>700</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1349,65 +1403,71 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1800</v>
       </c>
-      <c r="E18" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3">
         <v>-3000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3">
         <v>-2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-400</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-3600</v>
       </c>
       <c r="O18" s="3">
         <v>-3300</v>
       </c>
       <c r="P18" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="R18" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-3100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-2900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-700</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1417,8 +1477,14 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1443,64 +1509,66 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>-1800</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>1500</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
@@ -1511,62 +1579,68 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2100</v>
       </c>
-      <c r="E21" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>-3000</v>
       </c>
-      <c r="G21" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-400</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>-3400</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-2800</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1579,43 +1653,49 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>-300</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="G22" s="3">
-        <v>2400</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>-2200</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
-        <v>-100</v>
+        <v>-2200</v>
       </c>
       <c r="K22" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>-100</v>
       </c>
       <c r="M22" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N22" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1647,65 +1727,71 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1800</v>
       </c>
-      <c r="E23" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3">
         <v>-1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-3000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-2700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-3100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-2800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-600</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1715,8 +1801,14 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1747,11 +1839,11 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1783,8 +1875,14 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1851,65 +1949,71 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1800</v>
       </c>
-      <c r="E26" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3">
         <v>-1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-3000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-2700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-3100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-2800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-600</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1919,65 +2023,71 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="E27" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3">
         <v>-1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-3000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-2700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-3100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-2800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-600</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1987,8 +2097,14 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2055,8 +2171,14 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2123,8 +2245,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,8 +2319,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2259,64 +2393,70 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>1800</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
@@ -2327,65 +2467,71 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1800</v>
       </c>
-      <c r="E33" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3">
         <v>-900</v>
       </c>
-      <c r="G33" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3">
         <v>-1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-3000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-2700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-3100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-600</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2395,8 +2541,14 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2463,65 +2615,71 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1800</v>
       </c>
-      <c r="E35" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3">
         <v>-900</v>
       </c>
-      <c r="G35" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3">
         <v>-1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-3000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-2700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-3100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-600</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2531,70 +2689,76 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2604,8 +2768,14 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2630,8 +2800,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2656,59 +2828,61 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>700</v>
+      </c>
+      <c r="F41" s="3">
         <v>3400</v>
       </c>
-      <c r="E41" s="3">
-        <v>300</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H41" s="3">
         <v>1200</v>
       </c>
-      <c r="G41" s="3">
-        <v>700</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3">
         <v>2600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>7100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>8700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>11100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1000</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2724,8 +2898,14 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2751,26 +2931,26 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>3100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>3500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>4000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>6000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>5000</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2783,67 +2963,73 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
-      </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>800</v>
+      </c>
+      <c r="F43" s="3">
         <v>200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
+        <v>200</v>
+      </c>
+      <c r="K43" s="3">
+        <v>300</v>
+      </c>
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="M43" s="3">
+        <v>600</v>
+      </c>
+      <c r="N43" s="3">
+        <v>100</v>
+      </c>
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="P43" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q43" s="3">
         <v>200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="R43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
-        <v>400</v>
-      </c>
-      <c r="K43" s="3">
-        <v>600</v>
-      </c>
-      <c r="L43" s="3">
-        <v>100</v>
-      </c>
-      <c r="M43" s="3">
-        <v>400</v>
-      </c>
-      <c r="N43" s="3">
-        <v>700</v>
-      </c>
-      <c r="O43" s="3">
-        <v>200</v>
-      </c>
-      <c r="P43" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
+      <c r="S43" s="3">
+        <v>0</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
@@ -2860,20 +3046,26 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3">
         <v>700</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2892,11 +3084,11 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2928,8 +3120,14 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2942,14 +3140,14 @@
       <c r="F45" s="3">
         <v>0</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
         <v>0</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J45" s="3">
         <v>0</v>
@@ -2967,16 +3165,16 @@
         <v>0</v>
       </c>
       <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
+      <c r="R45" s="3">
+        <v>0</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
@@ -2990,65 +3188,71 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F46" s="3">
         <v>4400</v>
       </c>
-      <c r="E46" s="3">
-        <v>800</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H46" s="3">
         <v>1600</v>
       </c>
-      <c r="G46" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="3">
         <v>2900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>7600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>5000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>8900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>11100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>14000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>11400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1000</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3064,8 +3268,14 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3096,11 +3306,11 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -3132,31 +3342,37 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F48" s="3">
         <v>200</v>
       </c>
-      <c r="G48" s="3">
-        <v>200</v>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3">
         <v>200</v>
       </c>
-      <c r="I48" s="3">
-        <v>300</v>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K48" s="3">
         <v>300</v>
@@ -3174,16 +3390,16 @@
         <v>300</v>
       </c>
       <c r="P48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q48" s="3">
-        <v>0</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
+        <v>0</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
@@ -3200,8 +3416,14 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3214,14 +3436,14 @@
       <c r="F49" s="3">
         <v>0</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -3268,8 +3490,14 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3336,8 +3564,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3404,8 +3638,14 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3418,14 +3658,14 @@
       <c r="F52" s="3">
         <v>0</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3">
         <v>0</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
@@ -3442,20 +3682,20 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
+      <c r="S52" s="3">
+        <v>0</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
@@ -3472,8 +3712,14 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3540,59 +3786,65 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F54" s="3">
         <v>4600</v>
       </c>
-      <c r="E54" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H54" s="3">
         <v>1800</v>
       </c>
-      <c r="G54" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3">
         <v>3200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>5400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>7900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>5300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>7700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>9200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>11500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>14400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>11400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1100</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,8 +3860,14 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3634,8 +3892,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3660,58 +3920,60 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2400</v>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
-      </c>
-      <c r="M57" s="3">
-        <v>200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>100</v>
       </c>
       <c r="O57" s="3">
         <v>200</v>
       </c>
       <c r="P57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
+        <v>0</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
@@ -3728,44 +3990,50 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>100</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3">
         <v>100</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -3796,59 +4064,65 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>1100</v>
       </c>
       <c r="E59" s="3">
-        <v>2400</v>
-      </c>
-      <c r="F59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>2000</v>
       </c>
-      <c r="G59" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>1900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1400</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3">
         <v>600</v>
-      </c>
-      <c r="N59" s="3">
-        <v>600</v>
-      </c>
-      <c r="O59" s="3">
-        <v>1000</v>
       </c>
       <c r="P59" s="3">
         <v>600</v>
       </c>
       <c r="Q59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R59" s="3">
+        <v>600</v>
+      </c>
+      <c r="S59" s="3">
         <v>100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,59 +4138,65 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F60" s="3">
         <v>2000</v>
       </c>
-      <c r="E60" s="3">
-        <v>3800</v>
-      </c>
-      <c r="F60" s="3">
-        <v>3500</v>
-      </c>
-      <c r="G60" s="3">
-        <v>4500</v>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H60" s="3">
         <v>3500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K60" s="3">
         <v>2800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>100</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,8 +4212,14 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3947,13 +4233,13 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>100</v>
@@ -3965,19 +4251,19 @@
         <v>100</v>
       </c>
       <c r="M61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O61" s="3">
         <v>200</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
@@ -4000,8 +4286,14 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4014,42 +4306,42 @@
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="3">
-        <v>3800</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>1400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>6300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3">
         <v>400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1800</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4062,14 +4354,20 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
-      <c r="X62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4136,8 +4434,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4204,8 +4508,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4272,59 +4582,65 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F66" s="3">
         <v>2000</v>
       </c>
-      <c r="E66" s="3">
-        <v>3800</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H66" s="3">
         <v>3500</v>
       </c>
-      <c r="G66" s="3">
-        <v>8400</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3">
         <v>4900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>9400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>2400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>100</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4340,8 +4656,14 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4366,8 +4688,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4434,8 +4758,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4502,8 +4832,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4570,8 +4906,14 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4638,59 +4980,65 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-41400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-41400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-36700</v>
       </c>
-      <c r="E72" s="3">
-        <v>-34500</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3">
         <v>-32400</v>
       </c>
-      <c r="G72" s="3">
-        <v>-31500</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
         <v>-26100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-29100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-29900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-24700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-16000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-17600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-14600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-11200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-7500</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4706,8 +5054,14 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4774,8 +5128,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4842,8 +5202,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4910,59 +5276,65 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F76" s="3">
         <v>2600</v>
       </c>
-      <c r="E76" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H76" s="3">
         <v>-1700</v>
       </c>
-      <c r="G76" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J76" s="3">
         <v>-1800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-1500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>5800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>7800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>9800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>12100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>9000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4978,8 +5350,14 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5046,70 +5424,76 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5119,65 +5503,71 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1800</v>
       </c>
-      <c r="E81" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3">
         <v>-900</v>
       </c>
-      <c r="G81" s="3">
-        <v>-5400</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3">
         <v>-1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-3000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-2700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-3100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-600</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5187,8 +5577,14 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5213,8 +5609,10 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5248,26 +5646,26 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
@@ -5281,8 +5679,14 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5349,8 +5753,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5417,8 +5827,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5485,8 +5901,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5553,8 +5975,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5621,16 +6049,22 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2000</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
@@ -5656,26 +6090,26 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>-4300</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
@@ -5689,8 +6123,14 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5715,16 +6155,18 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
@@ -5747,11 +6189,11 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -5765,11 +6207,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
@@ -5783,8 +6225,14 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5851,8 +6299,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5919,16 +6373,22 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
@@ -5954,26 +6414,26 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
         <v>-6000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
@@ -5987,8 +6447,14 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6013,8 +6479,10 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6045,11 +6513,11 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -6081,8 +6549,14 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6149,8 +6623,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6217,8 +6697,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6285,16 +6771,22 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>700</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
@@ -6320,26 +6812,26 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>3700</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
@@ -6353,8 +6845,14 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6388,29 +6886,29 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
@@ -6418,64 +6916,70 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
       </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3">
         <v>-6700</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
@@ -6487,6 +6991,12 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NRSN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NRSN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="92">
   <si>
     <t>NRSN</t>
   </si>
@@ -656,106 +656,107 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -765,8 +766,14 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -803,11 +810,11 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -839,8 +846,14 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -913,8 +926,14 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -987,8 +1006,14 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,71 +1040,73 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F12" s="3">
         <v>1300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>1100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>2100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>3100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>2500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>2500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>500</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1089,8 +1116,14 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,8 +1196,14 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1201,11 +1240,11 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1237,8 +1276,14 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1311,8 +1356,14 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,71 +1387,73 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F17" s="3">
         <v>2300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
-      </c>
-      <c r="O17" s="3">
-        <v>3300</v>
-      </c>
-      <c r="P17" s="3">
-        <v>3600</v>
       </c>
       <c r="Q17" s="3">
         <v>3300</v>
       </c>
       <c r="R17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="S17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="T17" s="3">
         <v>5600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>700</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1410,71 +1463,77 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-2300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-3000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-2900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-3600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-400</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-3600</v>
       </c>
       <c r="Q18" s="3">
         <v>-3300</v>
       </c>
       <c r="R18" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="S18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="T18" s="3">
         <v>-5600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-3100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-2900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-700</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1484,8 +1543,14 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,70 +1577,72 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>-1800</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>1500</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
@@ -1586,68 +1653,74 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-2300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-2100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-3000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-2900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-3600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-400</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-4000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>-2800</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1660,8 +1733,14 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1672,37 +1751,37 @@
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>-300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>-2200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>-2200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>-100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>-100</v>
       </c>
       <c r="M22" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3">
         <v>-100</v>
       </c>
       <c r="O22" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P22" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1734,71 +1813,77 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2400</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-900</v>
       </c>
       <c r="H23" s="3">
         <v>-1800</v>
       </c>
       <c r="I23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K23" s="3">
         <v>-2700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-3900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-3000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-4000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-3100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-2800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-600</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,8 +1893,14 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1846,11 +1937,11 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1882,8 +1973,14 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,71 +2053,77 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2400</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-900</v>
       </c>
       <c r="H26" s="3">
         <v>-1800</v>
       </c>
       <c r="I26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K26" s="3">
         <v>-2700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-3900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-3000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-4000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-2800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-600</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2030,71 +2133,77 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-2400</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-900</v>
       </c>
       <c r="H27" s="3">
         <v>-1800</v>
       </c>
       <c r="I27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K27" s="3">
         <v>-2700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-3900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-3000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-4000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-2800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-600</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2104,8 +2213,14 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2293,14 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2373,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2453,14 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,70 +2533,76 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>1800</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-1500</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
@@ -2474,71 +2613,77 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-2400</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-900</v>
       </c>
       <c r="H33" s="3">
         <v>-1800</v>
       </c>
       <c r="I33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K33" s="3">
         <v>-2700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-3900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-3000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-4000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-2800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-600</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2548,8 +2693,14 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,71 +2773,77 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-2400</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-900</v>
       </c>
       <c r="H35" s="3">
         <v>-1800</v>
       </c>
       <c r="I35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K35" s="3">
         <v>-2700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-3900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-3000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-4000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-2800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-600</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2696,76 +2853,82 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2775,8 +2938,14 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2972,10 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,65 +3002,67 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>200</v>
+      </c>
+      <c r="F41" s="3">
         <v>700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>7100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>4800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>4400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>4300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>8700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>11100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1000</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2905,8 +3078,14 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2929,35 +3108,35 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>3500</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>3100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>3500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>4000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>6000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>5000</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2970,31 +3149,37 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>800</v>
-      </c>
-      <c r="F43" s="3">
-        <v>200</v>
-      </c>
-      <c r="G43" s="3">
-        <v>400</v>
       </c>
       <c r="H43" s="3">
         <v>200</v>
@@ -3003,40 +3188,40 @@
         <v>400</v>
       </c>
       <c r="J43" s="3">
+        <v>200</v>
+      </c>
+      <c r="K43" s="3">
+        <v>400</v>
+      </c>
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>300</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
+      <c r="U43" s="3">
+        <v>0</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
@@ -3053,26 +3238,32 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="D44" s="3">
+        <v>500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>500</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3">
         <v>700</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3091,11 +3282,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3127,8 +3318,14 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3172,16 +3369,16 @@
         <v>0</v>
       </c>
       <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
+      <c r="T45" s="3">
+        <v>0</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
@@ -3195,71 +3392,77 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>800</v>
+      </c>
+      <c r="F46" s="3">
         <v>1600</v>
-      </c>
-      <c r="E46" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F46" s="3">
-        <v>4400</v>
       </c>
       <c r="G46" s="3">
         <v>1600</v>
       </c>
       <c r="H46" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I46" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J46" s="3">
         <v>2900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>7600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>7400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>5100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>5000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>7400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>8900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>11100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>14000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>11400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1000</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,8 +3478,14 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3313,11 +3522,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3349,31 +3558,37 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>200</v>
+      </c>
+      <c r="F48" s="3">
         <v>100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>100</v>
-      </c>
-      <c r="F48" s="3">
-        <v>200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>200</v>
       </c>
       <c r="H48" s="3">
         <v>200</v>
       </c>
       <c r="I48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K48" s="3">
         <v>300</v>
@@ -3397,16 +3612,16 @@
         <v>300</v>
       </c>
       <c r="R48" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="S48" s="3">
-        <v>0</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3">
+        <v>0</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
@@ -3423,8 +3638,14 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3497,8 +3718,14 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3798,14 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,8 +3878,14 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3689,20 +3928,20 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
+      <c r="U52" s="3">
+        <v>0</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
@@ -3719,8 +3958,14 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,65 +4038,71 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F54" s="3">
         <v>1700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>4600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>3200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>7900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>7700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>5400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>7900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>5300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>7700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>9200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>11500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>14400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>11400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1100</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3867,8 +4118,14 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4152,10 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,64 +4182,66 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>800</v>
+      </c>
+      <c r="F57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
-      </c>
-      <c r="O57" s="3">
-        <v>200</v>
-      </c>
-      <c r="P57" s="3">
-        <v>100</v>
       </c>
       <c r="Q57" s="3">
         <v>200</v>
       </c>
       <c r="R57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S57" s="3">
-        <v>0</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
+        <v>0</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
@@ -3997,19 +4258,25 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
@@ -4027,20 +4294,20 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4071,28 +4338,34 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>1100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1100</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>2000</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1900</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -4100,36 +4373,36 @@
       <c r="K59" s="3">
         <v>1900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>1900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O59" s="3">
         <v>1400</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>600</v>
-      </c>
-      <c r="P59" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>1000</v>
       </c>
       <c r="R59" s="3">
         <v>600</v>
       </c>
       <c r="S59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T59" s="3">
+        <v>600</v>
+      </c>
+      <c r="U59" s="3">
         <v>100</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4145,65 +4418,71 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F60" s="3">
         <v>2200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,16 +4498,22 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -4237,10 +4522,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>100</v>
@@ -4258,19 +4543,19 @@
         <v>100</v>
       </c>
       <c r="O61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q61" s="3">
         <v>200</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -4293,8 +4578,14 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4310,45 +4601,45 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>1400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>6300</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>2700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>6300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>500</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1800</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4361,14 +4652,20 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4738,14 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4818,14 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,65 +4898,71 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F66" s="3">
         <v>2200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>9400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>9400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>2400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>100</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4663,8 +4978,14 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +5012,10 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +5088,14 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5168,14 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5248,14 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,65 +5328,71 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-47800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-47800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-41400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-41400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-36700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-32400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-26100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-29900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-16000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-29100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-29900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-24700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-16000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-17600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-14600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-11200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-8400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-7500</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5061,8 +5408,14 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5488,14 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5568,14 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,65 +5648,71 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F76" s="3">
         <v>-500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-1700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-1800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-1500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-1500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>2900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>5800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>7800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>9800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>12100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>9000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>900</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5357,8 +5728,14 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,76 +5808,82 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5510,71 +5893,77 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-2400</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-900</v>
       </c>
       <c r="H81" s="3">
         <v>-1800</v>
       </c>
       <c r="I81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K81" s="3">
         <v>-2700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-3900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-3000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-4000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-2800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-600</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5584,8 +5973,14 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,8 +6007,10 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5635,14 +6032,14 @@
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
@@ -5653,26 +6050,26 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
@@ -5686,8 +6083,14 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +6163,14 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6243,14 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6323,14 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6403,14 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,23 +6483,29 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-2000</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6097,26 +6530,26 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
@@ -6130,8 +6563,14 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,8 +6597,10 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6169,11 +6610,11 @@
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -6196,11 +6637,11 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -6214,11 +6655,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -6232,8 +6673,14 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6753,14 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,8 +6833,14 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6391,11 +6850,11 @@
       <c r="E94" s="3">
         <v>0</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -6421,26 +6880,26 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
@@ -6454,8 +6913,14 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6947,10 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6520,11 +6987,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6556,8 +7023,14 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +7103,14 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +7183,14 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,23 +7263,29 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6819,26 +7310,26 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>3700</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
@@ -6852,8 +7343,14 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6893,29 +7390,29 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
@@ -6923,26 +7420,32 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1400</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
@@ -6952,41 +7455,41 @@
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
+        <v>0</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
@@ -6998,6 +7501,12 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
